--- a/XLibur.Tests/Resource/Examples/Misc/AddingDataTableAsWorksheet.xlsx
+++ b/XLibur.Tests/Resource/Examples/Misc/AddingDataTableAsWorksheet.xlsx
@@ -435,9 +435,9 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="9.853482" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="11.282054" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="11.424911" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="9.710625" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="8.996339" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="9.282054" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:4">
